--- a/relatorio_novo.xlsx
+++ b/relatorio_novo.xlsx
@@ -8,8 +8,10 @@
   <sheets>
     <sheet name="Planilha1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="0" fullCalcOnLoad="1"/>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Planilha1'!$A$1:$F$1</definedName>
+  </definedNames>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -45,8 +47,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -424,12 +427,15 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F156"/>
+  <dimension ref="A1:F168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="10.85546875" customWidth="1" min="2" max="2"/>
     <col width="12.7109375" bestFit="1" customWidth="1" min="3" max="3"/>
     <col width="12" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="40.5703125" customWidth="1" min="5" max="5"/>
+    <col width="54.7109375" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -5306,7 +5312,381 @@
         </is>
       </c>
     </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>009/2023</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Poço do condominio Vila Toscana necessita de algumas adequações.</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>Obras paralisados</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Obras paralisados</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Vila toscana, poço operando, necessita de adequações. Poço almoxarifado - obra paralisada</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>017/2024</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Obras em atraso</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>Falta perfurar os poços Alto da Fé e do Complexo Carimã</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Obras em atraso</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>003/2024</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Obras em atraso</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>No assentamento Primavera, segundo a empresa falta o SANEAR realizar o rebaixamento de energia</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>A empresa apresentou os documentos exigidos em legislação e todos os 3 funcionarios utilizam os equipamentos de proteção individual</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Alguns dos poços que estão neste contrato estão em atraso. São execuções.</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>008/2023</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Não houve</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>Serviços paralisados</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Serviços paralisados</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Não houve</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>001/2025</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Não houve</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>Neste mês estive nos dias 08, 16 e 28 no local da reciclagem</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Mat. reciclado = 86, 1174 T (metal: 5,7T/papel: 69,9016T / plástico: 10,5158T)</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>PSAU R$ 17.646,81.  Neste mês trabalharam 21 cooperados</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>014/2025</t>
+        </is>
+      </c>
+      <c r="B162" s="1" t="n">
+        <v>45961</v>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Serviço prestado conforme cronograma</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Ordem de inicio dada em 02/10/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>014/2025</t>
+        </is>
+      </c>
+      <c r="B163" s="1" t="n">
+        <v>45989</v>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>Serviço prestado conforme cronograma</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Protocolada medicao 01 em 25/11/2026 no valor total do contrato</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>014/2025</t>
+        </is>
+      </c>
+      <c r="B164" s="1" t="n">
+        <v>46022</v>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>Serviço prestado conforme cronograma</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>NF  02 emititda em 04/12/2025 e paga em 19/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>014/2025</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>31/12/2025</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>Sem diligências</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>Serviço prestado conforme cronograma</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>NF 02 emitida em 04/12/2025 e paga em 19/12/2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>006/2024</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>30/01/2026</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Não houve</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>Estamos no aguardo dos documentos solicitados atraves dos memorandos</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>Dentro do cronograma do contrato</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Sem ocorrencias</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>034/2022</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>Serviço executado conforme demanda do setor de perdas</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Nenhum serviço foi executado ou medido no periodo</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>028/2023</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Serviço prestado conforme solicitação do SANEAR </t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>BM 20 protocolizado em 30/01/2026 no valor de R$ 35.089,76 e BM 21 protocolizado em 23/02/2026 no valor de R$ 23.842,17</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter ref="A1:F1"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
 </worksheet>
 </file>
--- a/relatorio_novo.xlsx
+++ b/relatorio_novo.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F168"/>
+  <dimension ref="A1:F174"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5685,6 +5685,198 @@
         </is>
       </c>
     </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>009/2022</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>Serviço prestado conforme Ordens de Serviços emitidas</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>BM 09 do 4° ADITIVO protocolizado em  27/02/2026  no valor de R$ 734.795,99</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>018/2024</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>Serviço prestado conforme cronograma</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Pagamento em 13/02/2026 a NF 332 referente ao BM 08  no valor de R$ 238.489,65.</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>007/2024</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Serviço prestado conforme solicitação do SANEAR </t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Em fase final de acabamento dos módulos de decantação. </t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>019/2025</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Serviço prestado conforme contrato</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Sem observação</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>018/2023</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Serviço pausado</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Vigencia do contrato venceu em 13/02/2026 e não foi renovado</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>010/2024</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Nenhum serviço prestado no periodo</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>SANEAR ainda não teve retorno da prefeitura sobre a  cessão de área para instalação da planta inteira da usina fotovoltaica</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>

--- a/relatorio_novo.xlsx
+++ b/relatorio_novo.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F176"/>
+  <dimension ref="A1:F182"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -5934,6 +5934,198 @@
         </is>
       </c>
     </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>007/2024</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Serviço prestado conforme solicitação do SANEAR </t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t xml:space="preserve">BM 18 protocolizado em 04/03/2026 no valor de R$ 170.056,62. </t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>010/2024</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Nenhum serviço prestado no periodo</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>SANEAR ainda não teve retorno da prefeitura sobre a  cessão de área para instalação da planta inteira da usina fotovoltaica</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>018/2024</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Serviço prestado conforme cronograma</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>BM 09  protocolizado em 12/03/2026 no valor de R$ 168.681,47</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>019/2025</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Serviço prestado conforme contrato</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>Sem observação</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>028/2023</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Serviço prestado conforme solicitação do SANEAR </t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>BM 22  protocolizado em 05/03/2026 no valor de R$ 65.166,97 e BM 23 protocolizado em 31/03/2026 no valor de R$ 42.382,32</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>034/2022</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>31/03/2026</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>Serviço executado conforme demanda do setor de perdas</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>Nenhum serviço foi executado ou medido no periodo</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>

--- a/relatorio_novo.xlsx
+++ b/relatorio_novo.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F182"/>
+  <dimension ref="A1:F184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6126,6 +6126,70 @@
         </is>
       </c>
     </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>009/2022</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>Serviço prestado conforme Ordens de Serviços emitidas</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>BM 11 do 4° ADITIVO protocolizado em  27/04/2026  no valor de R$ 305.368,88</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>007/2024</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Serviço prestado conforme solicitação do SANEAR </t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>Pagamento do BM 18 efetuado em 02/04/2026.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>

--- a/relatorio_novo.xlsx
+++ b/relatorio_novo.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F184"/>
+  <dimension ref="A1:F186"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6190,6 +6190,70 @@
         </is>
       </c>
     </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>018/2024</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>Serviço prestado conforme cronograma</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>Pagamento do BM 09 em 14/04/2026 através da NF 344 emitida em 08/04/2026.</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>019/2025</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>Serviço prestado conforme contrato</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>Sem observação</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>

--- a/relatorio_novo.xlsx
+++ b/relatorio_novo.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F186"/>
+  <dimension ref="A1:F187"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6254,6 +6254,38 @@
         </is>
       </c>
     </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>028/2023</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Serviço prestado conforme solicitação do SANEAR </t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>Pagamento do  BM 23 em  10/04/2026 através da nota fiscal 339 emitida em 09/04/2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>

--- a/relatorio_novo.xlsx
+++ b/relatorio_novo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{96C0FDAC-3A38-4F73-8A41-97D3808A7E54}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3531ADCB-A559-4D91-ABFB-EFBF7245B501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1104" uniqueCount="282">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="283">
   <si>
     <t>CONTRATO</t>
   </si>
@@ -876,6 +876,9 @@
   </si>
   <si>
     <t>021/2025</t>
+  </si>
+  <si>
+    <t>Sem obervacao</t>
   </si>
 </sst>
 </file>
@@ -4942,6 +4945,21 @@
       <c r="A190" t="s">
         <v>281</v>
       </c>
+      <c r="B190" s="1">
+        <v>46112</v>
+      </c>
+      <c r="C190" t="s">
+        <v>141</v>
+      </c>
+      <c r="D190" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" t="s">
+        <v>187</v>
+      </c>
+      <c r="F190" t="s">
+        <v>282</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/relatorio_novo.xlsx
+++ b/relatorio_novo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3531ADCB-A559-4D91-ABFB-EFBF7245B501}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BB8A72-51DE-4858-8B3C-4D4859A456D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1108" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="281">
   <si>
     <t>CONTRATO</t>
   </si>
@@ -873,12 +873,6 @@
   </si>
   <si>
     <t>Pagamento do  BM 23 em  10/04/2026 através da nota fiscal 339 emitida em 09/04/2026</t>
-  </si>
-  <si>
-    <t>021/2025</t>
-  </si>
-  <si>
-    <t>Sem obervacao</t>
   </si>
 </sst>
 </file>
@@ -4942,24 +4936,7 @@
       </c>
     </row>
     <row r="190" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A190" t="s">
-        <v>281</v>
-      </c>
-      <c r="B190" s="1">
-        <v>46112</v>
-      </c>
-      <c r="C190" t="s">
-        <v>141</v>
-      </c>
-      <c r="D190" t="s">
-        <v>9</v>
-      </c>
-      <c r="E190" t="s">
-        <v>187</v>
-      </c>
-      <c r="F190" t="s">
-        <v>282</v>
-      </c>
+      <c r="B190" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/relatorio_novo.xlsx
+++ b/relatorio_novo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9BB8A72-51DE-4858-8B3C-4D4859A456D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9FB3869-B829-40F4-9ADA-D0A0FBDF1FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1103" uniqueCount="281">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1119" uniqueCount="286">
   <si>
     <t>CONTRATO</t>
   </si>
@@ -873,6 +873,21 @@
   </si>
   <si>
     <t>Pagamento do  BM 23 em  10/04/2026 através da nota fiscal 339 emitida em 09/04/2026</t>
+  </si>
+  <si>
+    <t>021/2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Pagamento do BM 01 em 30/12/2025</t>
+  </si>
+  <si>
+    <t>Pagamento do BM 02 em 27/02/2026</t>
+  </si>
+  <si>
+    <t>Pagamento do BM 03 em 27/03/2026</t>
   </si>
 </sst>
 </file>
@@ -1225,7 +1240,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F190"/>
+  <dimension ref="A1:G193"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4675,7 +4690,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="177" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>42</v>
       </c>
@@ -4695,7 +4710,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="178" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>25</v>
       </c>
@@ -4715,7 +4730,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="179" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>67</v>
       </c>
@@ -4735,7 +4750,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="180" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>249</v>
       </c>
@@ -4755,7 +4770,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="181" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>39</v>
       </c>
@@ -4775,7 +4790,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="182" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>48</v>
       </c>
@@ -4795,7 +4810,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="183" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>35</v>
       </c>
@@ -4815,7 +4830,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="184" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>42</v>
       </c>
@@ -4835,7 +4850,7 @@
         <v>278</v>
       </c>
     </row>
-    <row r="185" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>67</v>
       </c>
@@ -4855,7 +4870,7 @@
         <v>279</v>
       </c>
     </row>
-    <row r="186" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>249</v>
       </c>
@@ -4875,7 +4890,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="187" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>39</v>
       </c>
@@ -4895,7 +4910,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="188" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>48</v>
       </c>
@@ -4915,7 +4930,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="189" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>25</v>
       </c>
@@ -4935,8 +4950,71 @@
         <v>252</v>
       </c>
     </row>
-    <row r="190" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="B190" s="1"/>
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A190" t="s">
+        <v>281</v>
+      </c>
+      <c r="B190" s="1">
+        <v>46021</v>
+      </c>
+      <c r="C190" t="s">
+        <v>141</v>
+      </c>
+      <c r="D190" t="s">
+        <v>9</v>
+      </c>
+      <c r="E190" t="s">
+        <v>81</v>
+      </c>
+      <c r="F190" t="s">
+        <v>283</v>
+      </c>
+      <c r="G190" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A191" t="s">
+        <v>281</v>
+      </c>
+      <c r="B191" s="1">
+        <v>46052</v>
+      </c>
+      <c r="C191" t="s">
+        <v>141</v>
+      </c>
+      <c r="D191" t="s">
+        <v>9</v>
+      </c>
+      <c r="E191" t="s">
+        <v>81</v>
+      </c>
+      <c r="F191" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A192" t="s">
+        <v>281</v>
+      </c>
+      <c r="B192" s="1">
+        <v>46080</v>
+      </c>
+      <c r="C192" t="s">
+        <v>141</v>
+      </c>
+      <c r="D192" t="s">
+        <v>9</v>
+      </c>
+      <c r="E192" t="s">
+        <v>81</v>
+      </c>
+      <c r="F192" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="193" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B193" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/relatorio_novo.xlsx
+++ b/relatorio_novo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B9FB3869-B829-40F4-9ADA-D0A0FBDF1FAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1F2CA9-E973-41AA-96DC-7DA3C2E32592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$F$1</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -878,10 +878,10 @@
     <t>021/2025</t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>Pagamento do BM 01 em 30/12/2025</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>Pagamento do BM 02 em 27/02/2026</t>
@@ -923,9 +923,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1244,7 +1245,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
-    <col min="2" max="2" width="10.85546875" customWidth="1"/>
+    <col min="2" max="2" width="27.7109375" customWidth="1"/>
     <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="12" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="40.5703125" customWidth="1"/>
@@ -4954,9 +4955,7 @@
       <c r="A190" t="s">
         <v>281</v>
       </c>
-      <c r="B190" s="1">
-        <v>46021</v>
-      </c>
+      <c r="B190" s="2"/>
       <c r="C190" t="s">
         <v>141</v>
       </c>
@@ -4967,19 +4966,17 @@
         <v>81</v>
       </c>
       <c r="F190" t="s">
+        <v>282</v>
+      </c>
+      <c r="G190" t="s">
         <v>283</v>
-      </c>
-      <c r="G190" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>281</v>
       </c>
-      <c r="B191" s="1">
-        <v>46052</v>
-      </c>
+      <c r="B191" s="2"/>
       <c r="C191" t="s">
         <v>141</v>
       </c>
@@ -4997,9 +4994,7 @@
       <c r="A192" t="s">
         <v>281</v>
       </c>
-      <c r="B192" s="1">
-        <v>46080</v>
-      </c>
+      <c r="B192" s="2"/>
       <c r="C192" t="s">
         <v>141</v>
       </c>
@@ -5014,7 +5009,7 @@
       </c>
     </row>
     <row r="193" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B193" s="1"/>
+      <c r="B193" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/relatorio_novo.xlsx
+++ b/relatorio_novo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A1F2CA9-E973-41AA-96DC-7DA3C2E32592}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60886AE9-993F-432C-A3AB-7332A8F19FF1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -923,10 +923,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1241,7 +1240,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:G193"/>
+  <dimension ref="A1:G192"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -4955,7 +4954,6 @@
       <c r="A190" t="s">
         <v>281</v>
       </c>
-      <c r="B190" s="2"/>
       <c r="C190" t="s">
         <v>141</v>
       </c>
@@ -4976,7 +4974,6 @@
       <c r="A191" t="s">
         <v>281</v>
       </c>
-      <c r="B191" s="2"/>
       <c r="C191" t="s">
         <v>141</v>
       </c>
@@ -4994,7 +4991,6 @@
       <c r="A192" t="s">
         <v>281</v>
       </c>
-      <c r="B192" s="2"/>
       <c r="C192" t="s">
         <v>141</v>
       </c>
@@ -5007,9 +5003,6 @@
       <c r="F192" t="s">
         <v>285</v>
       </c>
-    </row>
-    <row r="193" spans="2:2" x14ac:dyDescent="0.25">
-      <c r="B193" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>

--- a/relatorio_novo.xlsx
+++ b/relatorio_novo.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G193"/>
+  <dimension ref="A1:F193"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6376,7 +6376,6 @@
           <t>Pagamento do BM 01 em 30/12/2025</t>
         </is>
       </c>
-      <c r="G190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">

--- a/relatorio_novo.xlsx
+++ b/relatorio_novo.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F193"/>
+  <dimension ref="A1:F201"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6463,6 +6463,257 @@
         </is>
       </c>
     </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>028/2024</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Serviço prestado conforme Ordem de Serviço aberta pelo SANEAR</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>008/2023</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Não houve</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>Serviços paralisados</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Serviços paralisados</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>Vencimento deste contrato: 20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>009/2023</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Poço do condominio Vila Toscana necessita de algumas adequações.</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>Obras paralisadas</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>Obras paralisadas</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Contrato vence dia : 28/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>003/2024</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Obras em atraso</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>No assentamento Primavera, segundo a empresa falta o SANEAR realizar o rebaixamento de energia. No poço do distr. Razia, executou o barrilete da caixa d´agua</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>A empresa apresentou os documentos exigidos em legislação e todos os 3 funcionarios utilizam os equipamentos de proteção individual</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>Contrato com vencimento em : 25/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>014/2024</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Não ocorreu</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>Neste mês estive nos dias 13, 23 e 28 no local da reciclagem</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>Mat. reciclado = 65,2482 T (aluminio: 0,5924T/papel: 64,5T / metal: 0,1558T)</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Neste mês trabalharam 13 cooperados. PSAU R$ 14.301,50</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>017/2024</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Obras em atraso</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>Falta perfurar os poços Alto da Fé e do Complexo Carimã</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>Obras em atraso</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>Contrato com vencimento em: 15/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>001/2025</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Não houve</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>Neste mês estive nos dias 13, 23 e 28 no local da reciclagem</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>Mat. reciclado = 69, 3445 T (metal: 3,3875T/papel: 43,674T / plástico: 12,823T/vidro:9,46T)</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>PSAU R$ 14.210,08.  Neste mês trabalharam 23 cooperados</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>006/2024</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Aguardando informações solicitadas por oficio no dia 19/02/2026</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>Estamos no aguardo dos documentos solicitados atraves dos memorandos</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>No aguardo de informações da Coomser</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>Aguardando relatorio do mês, conforme solicitado por oficio numero 01/26 no dia 19/02/2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>

--- a/relatorio_novo.xlsx
+++ b/relatorio_novo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF877BC-56FB-4E80-9D47-FED212980589}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DEE85F4-5FF5-451F-A188-B544595A5DD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1172" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="304">
   <si>
     <t>CONTRATO</t>
   </si>
@@ -933,6 +933,15 @@
   </si>
   <si>
     <t>016/2025</t>
+  </si>
+  <si>
+    <t>A empresa contratada apresentou o 1° relatorio com pré relatório de regularização dos recursos hídricos subterrâneos e tamponamento definitivo de alguns poços tubulares</t>
+  </si>
+  <si>
+    <t>Dentro do cronograma</t>
+  </si>
+  <si>
+    <t>A empresa apresentou e recebeu a 1ª medição (N.F.)</t>
   </si>
 </sst>
 </file>
@@ -5227,8 +5236,20 @@
       <c r="A202" t="s">
         <v>300</v>
       </c>
-      <c r="B202" s="1">
-        <v>46142</v>
+      <c r="B202" t="s">
+        <v>276</v>
+      </c>
+      <c r="C202" t="s">
+        <v>135</v>
+      </c>
+      <c r="D202" t="s">
+        <v>301</v>
+      </c>
+      <c r="E202" t="s">
+        <v>302</v>
+      </c>
+      <c r="F202" t="s">
+        <v>303</v>
       </c>
     </row>
   </sheetData>

--- a/relatorio_novo.xlsx
+++ b/relatorio_novo.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F203"/>
+  <dimension ref="A1:F204"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6778,6 +6778,38 @@
         </is>
       </c>
     </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>016/2025</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Não houve</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>A empresa contratada apresentou o 1° relatorio com pré relatório de regularização dos recursos hídricos subterrâneos e tamponamento definitivo de alguns poços tubulares</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Dentro do cronograma</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>A empresa apresentou e recebeu a 1ª medição (N.F.)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>

--- a/relatorio_novo.xlsx
+++ b/relatorio_novo.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F204"/>
+  <dimension ref="A1:F205"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6810,6 +6810,38 @@
         </is>
       </c>
     </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>016/2025</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>30/04/2026</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Não houve</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>A empresa contratada apresentou o 1° relatorio com pré relatório de regularização dos recursos hídricos subterrâneos e tamponamento definitivo de alguns poços tubulares</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Dentro do cronograma</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>A empresa apresentou e recebeu a 1ª medição (N.F.)</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>

--- a/relatorio_novo.xlsx
+++ b/relatorio_novo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE123551-1A16-44DC-8F8F-F977CF099AD9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DD07AF-6F2F-4319-BB25-1B4061BD00C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,12 +18,12 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$F$1</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1177" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="308">
   <si>
     <t>CONTRATO</t>
   </si>
@@ -942,6 +942,18 @@
   </si>
   <si>
     <t>A empresa apresentou e recebeu a 1ª medição (N.F.)</t>
+  </si>
+  <si>
+    <t>005/2026</t>
+  </si>
+  <si>
+    <t>008/2026</t>
+  </si>
+  <si>
+    <t>009/2026</t>
+  </si>
+  <si>
+    <t>010/2026</t>
   </si>
 </sst>
 </file>
@@ -1294,7 +1306,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F202"/>
+  <dimension ref="A1:F206"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -5252,6 +5264,26 @@
         <v>303</v>
       </c>
     </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A203" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A204" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A205" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A206" t="s">
+        <v>307</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/relatorio_novo.xlsx
+++ b/relatorio_novo.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marcos.brumatti\Documents\GitHub\patrimonio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F8DD07AF-6F2F-4319-BB25-1B4061BD00C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A6575BF2-7F2F-457C-923E-1FC50A11DE80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1181" uniqueCount="308">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1182" uniqueCount="309">
   <si>
     <t>CONTRATO</t>
   </si>
@@ -954,6 +954,9 @@
   </si>
   <si>
     <t>010/2026</t>
+  </si>
+  <si>
+    <t>003/2026</t>
   </si>
 </sst>
 </file>
@@ -1306,7 +1309,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F206"/>
+  <dimension ref="A1:F207"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -5284,6 +5287,11 @@
         <v>307</v>
       </c>
     </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A207" t="s">
+        <v>308</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.78740157499999996" bottom="0.78740157499999996" header="0.31496062000000002" footer="0.31496062000000002"/>

--- a/relatorio_novo.xlsx
+++ b/relatorio_novo.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F208"/>
+  <dimension ref="A1:F216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6813,6 +6813,262 @@
         </is>
       </c>
     </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>017/2024</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Obras em atraso</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>Falta perfurar os poços Alto da Fé e do Complexo Carimã</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>Obras em atraso</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>Contrato com vencimento em: 15/07/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>009/2023</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Poço do condominio Vila Toscana necessita de algumas adequações.</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>Obras paralisadas</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>Obras paralisadas</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>Contrato vence dia : 28/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>008/2023</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Não houve</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>Serviços paralisados</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>Serviços paralisados</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>Vencimento deste contrato: 20/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>006/2024</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Aguardando informações solicitadas por oficio no dia 19/02/2026</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>Estamos no aguardo dos documentos solicitados atraves dos memorandos</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>No aguardo de informações da Coomser</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Aguardando relatorio do mês, conforme solicitado por oficio numero 01/26 no dia 19/02/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>003/2024</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Obras em atraso</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>No assentamento Primavera, segundo a empresa falta o SANEAR realizar o rebaixamento de energia. No poço do distr. Razia, executou o barrilete da caixa d´agua. Poço resistencia está em funcionamento e poço marajá falta descer a bomba.</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>A empresa apresentou os documentos exigidos em legislação e todos os 3 funcionarios utilizam os equipamentos de proteção individual</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>Contrato com vencimento em : 25/05/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>001/2025</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Não houve</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>Neste mês estive nos dias 05, 19 e 25 no local da reciclagem</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Mat. reciclado = 76,74 T (metal: 4,86T/papel: 58,58T / plástico: 6,77T/vidro:6,53T)</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>PSAU R$ 15.760,58.  Neste mês trabalharam 21 cooperados</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>016/2025</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Não houve</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>A empresa contratada apresentou o 1° relatorio com pré relatório de regularização dos recursos hídricos subterrâneos e tamponamento definitivo de alguns poços tubulares</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Dentro do cronograma</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>Dentro das conformidades</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>014/2024</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>27/02/2026</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Não ocorreu</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>Neste mês estive nos dias 05, 19 e 25 no local da reciclagem</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Mat. reciclado = 64,65 T (metal: 2,05T/papel: 59,13T / plástico: 3,47T)</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
+        <is>
+          <t xml:space="preserve"> Neste mês trabalharam 13 cooperados. PSAU R$ 13.248,94</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>

--- a/relatorio_novo.xlsx
+++ b/relatorio_novo.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F245"/>
+  <dimension ref="A1:F258"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -7972,6 +7972,422 @@
         </is>
       </c>
     </row>
+    <row r="246">
+      <c r="A246" t="inlineStr">
+        <is>
+          <t>004/2026</t>
+        </is>
+      </c>
+      <c r="B246" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="C246" t="inlineStr">
+        <is>
+          <t>Sem ocorrencias</t>
+        </is>
+      </c>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E246" t="inlineStr">
+        <is>
+          <t>Serviço prestado conforme cronograma e ordens de serviço expedidas</t>
+        </is>
+      </c>
+      <c r="F246" t="inlineStr">
+        <is>
+          <t>BM 01 protocolizada em 30/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t>034/2022</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D247" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E247" t="inlineStr">
+        <is>
+          <t>Serviço executado conforme demanda do setor de perdas</t>
+        </is>
+      </c>
+      <c r="F247" t="inlineStr">
+        <is>
+          <t>Encaminhada ordem de execução de serviço no residencial Altamirando através do OFICIO DIRTEC/ENG N° 126/2026 de 22/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="248">
+      <c r="A248" t="inlineStr">
+        <is>
+          <t>028/2023</t>
+        </is>
+      </c>
+      <c r="B248" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="C248" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D248" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E248" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Serviço prestado conforme solicitação do SANEAR </t>
+        </is>
+      </c>
+      <c r="F248" t="inlineStr">
+        <is>
+          <t>BM 24 protocolizado em 08/06/2026 no valor de R$ 31.601,21 e pago em 12/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="249">
+      <c r="A249" t="inlineStr">
+        <is>
+          <t>005/2026</t>
+        </is>
+      </c>
+      <c r="B249" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="C249" t="inlineStr">
+        <is>
+          <t>Contrato assinado em 04/05/2026</t>
+        </is>
+      </c>
+      <c r="D249" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E249" t="inlineStr">
+        <is>
+          <t>Sem avaliação</t>
+        </is>
+      </c>
+      <c r="F249" t="inlineStr">
+        <is>
+          <t>Aguardan autorização da CEF para dar ordem de inicio da obra</t>
+        </is>
+      </c>
+    </row>
+    <row r="250">
+      <c r="A250" t="inlineStr">
+        <is>
+          <t>018/2024</t>
+        </is>
+      </c>
+      <c r="B250" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="C250" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D250" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E250" t="inlineStr">
+        <is>
+          <t>Serviço prestado conforme cronograma</t>
+        </is>
+      </c>
+      <c r="F250" t="inlineStr">
+        <is>
+          <t>BM 10 protocolizado em 12/06/2026 no valor de R$ 124.700,33</t>
+        </is>
+      </c>
+    </row>
+    <row r="251">
+      <c r="A251" t="inlineStr">
+        <is>
+          <t>008/2026</t>
+        </is>
+      </c>
+      <c r="B251" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="C251" t="inlineStr">
+        <is>
+          <t>Contrato assinado em 20/05/2026</t>
+        </is>
+      </c>
+      <c r="D251" t="inlineStr">
+        <is>
+          <t>Sem diligências</t>
+        </is>
+      </c>
+      <c r="E251" t="inlineStr">
+        <is>
+          <t>Sem avaliação</t>
+        </is>
+      </c>
+      <c r="F251" t="inlineStr">
+        <is>
+          <t>Aguardando autorização da CEf para dar ordem de inicio de obra</t>
+        </is>
+      </c>
+    </row>
+    <row r="252">
+      <c r="A252" t="inlineStr">
+        <is>
+          <t>007/2024</t>
+        </is>
+      </c>
+      <c r="B252" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="C252" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D252" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E252" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Serviço prestado conforme solicitação do SANEAR </t>
+        </is>
+      </c>
+      <c r="F252" t="inlineStr">
+        <is>
+          <t>Término dos trabalhos de parametrização das valvulas dos filtros e serviço de compartimentação do decantador. Testes de estanqueidade realizados .SErviços de parametrização serão refeitos e alguns vazamentos serão sanados.</t>
+        </is>
+      </c>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t>028/2024</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D253" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E253" t="inlineStr">
+        <is>
+          <t>Serviço prestado conforme Ordem de Serviço aberta pelo SANEAR</t>
+        </is>
+      </c>
+      <c r="F253" t="inlineStr">
+        <is>
+          <t>Sem observações</t>
+        </is>
+      </c>
+    </row>
+    <row r="254">
+      <c r="A254" t="inlineStr">
+        <is>
+          <t>019/2025</t>
+        </is>
+      </c>
+      <c r="B254" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="C254" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E254" t="inlineStr">
+        <is>
+          <t>Serviço prestado conforme contrato</t>
+        </is>
+      </c>
+      <c r="F254" t="inlineStr">
+        <is>
+          <t>Sem observação</t>
+        </is>
+      </c>
+    </row>
+    <row r="255">
+      <c r="A255" t="inlineStr">
+        <is>
+          <t>010/2026</t>
+        </is>
+      </c>
+      <c r="B255" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="C255" t="inlineStr">
+        <is>
+          <t>Contrato assinado em 20/05/2026</t>
+        </is>
+      </c>
+      <c r="D255" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="E255" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="F255" t="inlineStr">
+        <is>
+          <t>Pagamento da NF 12 em 12/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="256">
+      <c r="A256" t="inlineStr">
+        <is>
+          <t>010/2024</t>
+        </is>
+      </c>
+      <c r="B256" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="C256" t="inlineStr">
+        <is>
+          <t>Sem ocorrências</t>
+        </is>
+      </c>
+      <c r="D256" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E256" t="inlineStr">
+        <is>
+          <t>Nenhum serviço prestado no periodo</t>
+        </is>
+      </c>
+      <c r="F256" t="inlineStr">
+        <is>
+          <t xml:space="preserve">O contrato será aditivado por igual periodo. </t>
+        </is>
+      </c>
+    </row>
+    <row r="257">
+      <c r="A257" t="inlineStr">
+        <is>
+          <t>009/2026</t>
+        </is>
+      </c>
+      <c r="B257" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="C257" t="inlineStr">
+        <is>
+          <t>Sem ocorrencias</t>
+        </is>
+      </c>
+      <c r="D257" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E257" t="inlineStr">
+        <is>
+          <t>Sem avaliação</t>
+        </is>
+      </c>
+      <c r="F257" t="inlineStr">
+        <is>
+          <t>Solicitação de empenho no valor de R$ 26.297,20  no dia 23/06/2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="258">
+      <c r="A258" t="inlineStr">
+        <is>
+          <t>009/2022</t>
+        </is>
+      </c>
+      <c r="B258" t="inlineStr">
+        <is>
+          <t>30/06/2026</t>
+        </is>
+      </c>
+      <c r="C258" t="inlineStr">
+        <is>
+          <t>Contrato renovado em 08/05/2026 até 07/05/2027</t>
+        </is>
+      </c>
+      <c r="D258" t="inlineStr">
+        <is>
+          <t>Sem diligencias</t>
+        </is>
+      </c>
+      <c r="E258" t="inlineStr">
+        <is>
+          <t>Serviço prestado conforme Ordens de Serviços emitidas</t>
+        </is>
+      </c>
+      <c r="F258" t="inlineStr">
+        <is>
+          <t>BM 03 do 5° ADITIVO protocolizado em  25/06/2026  no valor de R$ 538.184,49</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:F1"/>
   <pageMargins left="0.511811024" right="0.511811024" top="0.787401575" bottom="0.787401575" header="0.31496062" footer="0.31496062"/>
